--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Documents\Av.01\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785D9F35-1164-4645-91FA-F3A940970591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52392D31-8066-4D88-B3C5-28704C478E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5688" yWindow="708" windowWidth="17280" windowHeight="11532" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="631">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1709,7 +1709,244 @@
     <t>Escolhe o Horario do filme desejado com definição com o valor do ingresso</t>
   </si>
   <si>
-    <t>1° Sessão, Cadeira 4, 222.923.422-05</t>
+    <t>Primeira etapa foi clicar no horario filme ( 14:00 2D, depois selecionar o Assento 03 C para o teste funcional, Acrescentar o valor do ingresso ( 1 ), Assim de rodar a operação o teste vai ser analisado.</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gimini </t>
+  </si>
+  <si>
+    <t>O tempo de um Sistema precisa ser de 2 segundos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isso foi um metodo criado para fazer um calculo dentro do sistema ( Caixa Preta ) para que o sistema aceite 1000 vezes a operação sem travamento </t>
+  </si>
+  <si>
+    <t>Retorno de um sistema funcional sem problemas na etapa da regra de negocios</t>
+  </si>
+  <si>
+    <t>O usuario poderar testar o Site sem ter problemas de travamento  ou demora no carregamento</t>
+  </si>
+  <si>
+    <t>Sistema de Acessibilidade do Site</t>
+  </si>
+  <si>
+    <t>Rodagem da tela com tempo de -3segundos por tela.</t>
+  </si>
+  <si>
+    <t>Filme: Órbita Silenciosa. Sessão: orb-1400 (14:00).</t>
+  </si>
+  <si>
+    <t>A sessão é destacada como ativa e o resumo exibe "Órbita Silenciosa · 14:00 · 2D".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor cobrado errado </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Selecionar o assento C1. 2. Preencher dados do cliente. 3. Selecionar Cartão.</t>
+  </si>
+  <si>
+    <t>1. Selecionar sessão orb-2030 (20:30). 2. Selecionar assento A3.</t>
+  </si>
+  <si>
+    <t>1. Selecionar sessão qui-1530 (15:30, 3D). 2. Selecionar assento B2.</t>
+  </si>
+  <si>
+    <t>1. Clicar no assento A1.</t>
+  </si>
+  <si>
+    <t>1. Digitar "1" no campo de meia-entrada.</t>
+  </si>
+  <si>
+    <t>1. Informar quantidade 2 para "Pipoca grande". 2. Informar quantidade 1 para "Refrigerante 500 ml".</t>
+  </si>
+  <si>
+    <t>1. Verificar resumo de valores.</t>
+  </si>
+  <si>
+    <t>1. Digitar "CINE10" no cupom. 2. Clicar em "Aplicar".</t>
+  </si>
+  <si>
+    <t>1. Digitar "CUPOMINVALIDO". 2. Clicar em "Aplicar".</t>
+  </si>
+  <si>
+    <t>1. Selecionar a opção de pagamento "Pix".</t>
+  </si>
+  <si>
+    <t>1. Preencher nome como "An". 2. Preencher CPF e e-mail válidos. 3. Clicar em "Confirmar compra".</t>
+  </si>
+  <si>
+    <t>1. Preencher CPF com "12345678". 2. Clicar em "Confirmar compra".</t>
+  </si>
+  <si>
+    <t>1. Clicar em "Confirmar compra" com todos os dados válidos.</t>
+  </si>
+  <si>
+    <t>Partição de Equivalência</t>
+  </si>
+  <si>
+    <t>Valor do ingresso para sessão até 17h</t>
+  </si>
+  <si>
+    <t>Valor do ingresso para sessão após 17h</t>
+  </si>
+  <si>
+    <t>Adicional de formato 3D no ingresso</t>
+  </si>
+  <si>
+    <t>Impedir seleção de assento ocupado</t>
+  </si>
+  <si>
+    <t>Aplicação de desconto de meia-entrada</t>
+  </si>
+  <si>
+    <t>Meia-entrada desativada em pré-estreia</t>
+  </si>
+  <si>
+    <t>Adição de produtos da bomboniere</t>
+  </si>
+  <si>
+    <t>Cálculo da taxa de conveniência</t>
+  </si>
+  <si>
+    <t>Aplicação do cupom CINE10</t>
+  </si>
+  <si>
+    <t>Rejeição de cupom inválido</t>
+  </si>
+  <si>
+    <t>Desconto de 5% para pagamento via Pix</t>
+  </si>
+  <si>
+    <t>Validação de nome inválido no checkout</t>
+  </si>
+  <si>
+    <t>Validação de CPF com digitação incorreta</t>
+  </si>
+  <si>
+    <t>Gravação de histórico e ocupação de assentos</t>
+  </si>
+  <si>
+    <t>Sistema aberto no navegador.</t>
+  </si>
+  <si>
+    <t>Sessão orb-1400 selecionada.</t>
+  </si>
+  <si>
+    <t>Sessão orb-1400 selecionada. Assento A1 ocupado.</t>
+  </si>
+  <si>
+    <t>Sessão far-2100 selecionada. Dois assentos escolhidos (A1 e A2).</t>
+  </si>
+  <si>
+    <t>Sessão vid-2200 (pré-estreia) selecionada. Um assento A1 escolhido.</t>
+  </si>
+  <si>
+    <t>Sessão e assentos selecionados.</t>
+  </si>
+  <si>
+    <t>1 ingresso selecionado. Dois produtos na bomboniere.</t>
+  </si>
+  <si>
+    <t>Sessão selecionada. Subtotal de ingressos + bomboniere = R$ 100,00.</t>
+  </si>
+  <si>
+    <t>Qualquer estado do pedido.</t>
+  </si>
+  <si>
+    <t>Pedido com subtotal parcial de R$ 50,00.</t>
+  </si>
+  <si>
+    <t>Sessão, assento e pagamento selecionados.</t>
+  </si>
+  <si>
+    <t>Dados preenchidos no checkout.</t>
+  </si>
+  <si>
+    <t>Pedido válido completo.</t>
+  </si>
+  <si>
+    <t>Assento: C1. Quantidade: 1 ingresso inteira.</t>
+  </si>
+  <si>
+    <t>Preço base do ingresso de R$ 24,00. Subtotal de ingressos = R$ 24,00.</t>
+  </si>
+  <si>
+    <t>Filme: Órbita Silenciosa. Sessão: 20:30. Assento: A3.</t>
+  </si>
+  <si>
+    <t>Preço base do ingresso de R$ 32,00. Subtotal = R$ 32,00, sem taxa 3D.</t>
+  </si>
+  <si>
+    <t>Sessão 3D das 15:30. 1 assento.</t>
+  </si>
+  <si>
+    <t>Ingresso calculado como R$ 24,00 + R$ 6,00 (3D) = R$ 30,00.</t>
+  </si>
+  <si>
+    <t>Assento: A1 (ocupado).</t>
+  </si>
+  <si>
+    <t>O assento não altera para o estado "selecionado" e o resumo continua inalterado.</t>
+  </si>
+  <si>
+    <t>Meia-entrada: 1. Inteiras: 1.</t>
+  </si>
+  <si>
+    <t>1 inteira = R$ 32,00. 1 meia = R$ 19,20. Total de ingressos = R$ 51,20.</t>
+  </si>
+  <si>
+    <t>Sessão: pré-estreia. Meias: 1.</t>
+  </si>
+  <si>
+    <t>Meia-entrada ignorada (0 meias consideradas). Valor cobrado de uma inteira = R$ 32,00.</t>
+  </si>
+  <si>
+    <t>Pipoca G: 2 × R$ 22,00. Refrigerante: 1 × R$ 9,50.</t>
+  </si>
+  <si>
+    <t>Subtotal da bomboniere = R$ 53,50 (R$ 44,00 + R$ 9,50).</t>
+  </si>
+  <si>
+    <t>Pagamento: Pix. Subtotal: R$ 50,00.</t>
+  </si>
+  <si>
+    <t>Desconto Pix de R$ 2,50 (5%) exibido e subtraído do valor total.</t>
+  </si>
+  <si>
+    <t>1. Selecionar o assento C1. 2. Preencher dados do cliente. 3. Selecionar Cartão.</t>
+  </si>
+  <si>
+    <t>Taxa de conveniência = (1 + 2) × R$ 2,50 = R$ 7,50.</t>
+  </si>
+  <si>
+    <t>Exibir mensagem "Cupom CINE10 aplicado." com estilo verde. Aplicar desconto de R$ 10,00 (10%).</t>
+  </si>
+  <si>
+    <t>Exibir mensagem "Cupom inválido." com estilo de erro. Nenhum desconto é computado.</t>
+  </si>
+  <si>
+    <t>Exibir mensagem "Informe o nome completo (mínimo de 3 letras)." e impedir a finalização da compra.</t>
+  </si>
+  <si>
+    <t>Exibir mensagem "Informe um CPF válido, com 11 dígitos." e impedir a finalização da compra.</t>
+  </si>
+  <si>
+    <t>Após 1,5s, exibir confirmação com código CL...; salvar pedido no localStorage e marcar assentos como ocupados no mapa.</t>
+  </si>
+  <si>
+    <t>Execultado e Correto</t>
+  </si>
+  <si>
+    <t>Valor cobrado errado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendente </t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
 </sst>
 </file>
@@ -1859,9 +2096,6 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1907,6 +2141,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2182,206 +2419,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2407,334 +2644,334 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -2789,100 +3026,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2925,263 +3162,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Falhou")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Bloqueado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Não executado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Alta")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <f>COUNTIF('6_Bugs'!N6:N35,"Corrigido*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <f>COUNTIF('7_Nao_Funcionais'!H6:H20,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="9" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="9" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="10" t="s">
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="9" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3229,211 +3466,219 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3462,382 +3707,382 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>494</v>
       </c>
     </row>
@@ -3857,90 +4102,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <v>46323</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="22">
         <v>0.84722222222222221</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3965,138 +4210,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>499</v>
       </c>
     </row>
@@ -4143,184 +4388,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4363,250 +4608,250 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="9"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C28" s="9"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C30" s="9"/>
+      <c r="C30" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4660,946 +4905,1278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-    </row>
-    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+    </row>
+    <row r="6" spans="1:15" ht="66" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="F9" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-    </row>
-    <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E14" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>551</v>
-      </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="E20" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5679,678 +6256,678 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="14" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6436,300 +7013,316 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="C6" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6788,356 +7381,356 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
